--- a/Ground Truth/ground_truth_shower.xlsx
+++ b/Ground Truth/ground_truth_shower.xlsx
@@ -766,7 +766,7 @@
         <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -900,7 +900,7 @@
         <v>0.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1101,7 +1101,7 @@
         <v>0.93</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1570,7 +1570,7 @@
         <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6994999999999999</v>
+        <v>0.6995</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         <v>0.64</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8119999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1905,7 +1905,7 @@
         <v>0.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7999999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
@@ -1972,7 +1972,7 @@
         <v>0.22</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P23" t="n">
         <v>2</v>
@@ -2039,7 +2039,7 @@
         <v>0.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2240,7 +2240,7 @@
         <v>0.46</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6994999999999999</v>
+        <v>0.6995</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         <v>0.52</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="P39" t="n">
         <v>2</v>
@@ -3446,7 +3446,7 @@
         <v>0.67</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
@@ -3848,7 +3848,7 @@
         <v>0.76</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0.67</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4183,7 +4183,7 @@
         <v>0.15</v>
       </c>
       <c r="O56" t="n">
-        <v>0.6724999999999999</v>
+        <v>0.6725</v>
       </c>
       <c r="P56" t="n">
         <v>3</v>
@@ -4317,7 +4317,7 @@
         <v>0.15</v>
       </c>
       <c r="O58" t="n">
-        <v>0.6854999999999999</v>
+        <v>0.6855</v>
       </c>
       <c r="P58" t="n">
         <v>2</v>
@@ -4585,7 +4585,7 @@
         <v>0.46</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5549999999999999</v>
+        <v>0.555</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4853,7 +4853,7 @@
         <v>0.76</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -4920,7 +4920,7 @@
         <v>0.93</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7105000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -5456,7 +5456,7 @@
         <v>0.31</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5005000000000001</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
@@ -5590,7 +5590,7 @@
         <v>0.22</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -5657,7 +5657,7 @@
         <v>0.46</v>
       </c>
       <c r="O78" t="n">
-        <v>0.7370000000000001</v>
+        <v>0.737</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
@@ -5791,7 +5791,7 @@
         <v>0.29</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
@@ -6193,7 +6193,7 @@
         <v>0.15</v>
       </c>
       <c r="O86" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6327,7 +6327,7 @@
         <v>0.57</v>
       </c>
       <c r="O88" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6461,7 +6461,7 @@
         <v>0.57</v>
       </c>
       <c r="O90" t="n">
-        <v>0.7174999999999999</v>
+        <v>0.7175</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         <v>0.35</v>
       </c>
       <c r="O92" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P92" t="n">
         <v>2</v>
@@ -6796,7 +6796,7 @@
         <v>0.35</v>
       </c>
       <c r="O95" t="n">
-        <v>0.6789999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -6997,7 +6997,7 @@
         <v>0.35</v>
       </c>
       <c r="O98" t="n">
-        <v>0.7394999999999999</v>
+        <v>0.7395</v>
       </c>
       <c r="P98" t="n">
         <v>2</v>
@@ -7466,7 +7466,7 @@
         <v>0.46</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7533,7 +7533,7 @@
         <v>0.67</v>
       </c>
       <c r="O106" t="n">
-        <v>0.5125000000000001</v>
+        <v>0.5125</v>
       </c>
       <c r="P106" t="n">
         <v>3</v>
@@ -7801,7 +7801,7 @@
         <v>0.46</v>
       </c>
       <c r="O110" t="n">
-        <v>0.5920000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -8002,7 +8002,7 @@
         <v>0.46</v>
       </c>
       <c r="O113" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         <v>0.57</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6190000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         <v>0.67</v>
       </c>
       <c r="O115" t="n">
-        <v>0.5265000000000001</v>
+        <v>0.5265</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8538,7 +8538,7 @@
         <v>0.67</v>
       </c>
       <c r="O121" t="n">
-        <v>0.5255000000000001</v>
+        <v>0.5255</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
@@ -8672,7 +8672,7 @@
         <v>0.46</v>
       </c>
       <c r="O123" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
@@ -9074,7 +9074,7 @@
         <v>0.46</v>
       </c>
       <c r="O129" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
       <c r="P129" t="n">
         <v>2</v>
@@ -9275,7 +9275,7 @@
         <v>0.76</v>
       </c>
       <c r="O132" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -9342,7 +9342,7 @@
         <v>0.67</v>
       </c>
       <c r="O133" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -9476,7 +9476,7 @@
         <v>0.46</v>
       </c>
       <c r="O135" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="P135" t="n">
         <v>2</v>
@@ -9811,7 +9811,7 @@
         <v>0.15</v>
       </c>
       <c r="O140" t="n">
-        <v>0.6034999999999999</v>
+        <v>0.6035</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
@@ -10012,7 +10012,7 @@
         <v>0.15</v>
       </c>
       <c r="O143" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
       <c r="P143" t="n">
         <v>2</v>
@@ -10213,7 +10213,7 @@
         <v>0.64</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0.35</v>
       </c>
       <c r="O149" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P149" t="n">
         <v>1</v>
@@ -10749,7 +10749,7 @@
         <v>0.67</v>
       </c>
       <c r="O154" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10816,7 +10816,7 @@
         <v>0.15</v>
       </c>
       <c r="O155" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="P155" t="n">
         <v>1</v>
@@ -11151,7 +11151,7 @@
         <v>0.67</v>
       </c>
       <c r="O160" t="n">
-        <v>0.5255000000000001</v>
+        <v>0.5255</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
@@ -11486,7 +11486,7 @@
         <v>0.46</v>
       </c>
       <c r="O165" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="P165" t="n">
         <v>2</v>
@@ -11620,7 +11620,7 @@
         <v>0.22</v>
       </c>
       <c r="O167" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P167" t="n">
         <v>2</v>
@@ -11687,7 +11687,7 @@
         <v>0.35</v>
       </c>
       <c r="O168" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
       <c r="P168" t="n">
         <v>3</v>
@@ -11955,7 +11955,7 @@
         <v>0.46</v>
       </c>
       <c r="O172" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="P172" t="n">
         <v>3</v>
@@ -12022,7 +12022,7 @@
         <v>0.22</v>
       </c>
       <c r="O173" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="P173" t="n">
         <v>1</v>
@@ -12156,7 +12156,7 @@
         <v>0.46</v>
       </c>
       <c r="O175" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="P175" t="n">
         <v>3</v>
@@ -12223,7 +12223,7 @@
         <v>0.22</v>
       </c>
       <c r="O176" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P176" t="n">
         <v>1</v>
@@ -12491,7 +12491,7 @@
         <v>0.5</v>
       </c>
       <c r="O180" t="n">
-        <v>0.7699999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
@@ -12558,7 +12558,7 @@
         <v>0.85</v>
       </c>
       <c r="O181" t="n">
-        <v>0.7749999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -12692,7 +12692,7 @@
         <v>0.5</v>
       </c>
       <c r="O183" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
@@ -12759,7 +12759,7 @@
         <v>0.85</v>
       </c>
       <c r="O184" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="P184" t="n">
         <v>3</v>
@@ -13161,7 +13161,7 @@
         <v>0.15</v>
       </c>
       <c r="O190" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
@@ -13228,7 +13228,7 @@
         <v>0.22</v>
       </c>
       <c r="O191" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="P191" t="n">
         <v>1</v>
@@ -13965,7 +13965,7 @@
         <v>0.31</v>
       </c>
       <c r="O202" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
@@ -14233,7 +14233,7 @@
         <v>0.22</v>
       </c>
       <c r="O206" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
@@ -14367,7 +14367,7 @@
         <v>0.46</v>
       </c>
       <c r="O208" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
@@ -14434,7 +14434,7 @@
         <v>0.22</v>
       </c>
       <c r="O209" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="P209" t="n">
         <v>3</v>
@@ -14501,7 +14501,7 @@
         <v>0.35</v>
       </c>
       <c r="O210" t="n">
-        <v>0.7905000000000001</v>
+        <v>0.7905</v>
       </c>
       <c r="P210" t="n">
         <v>2</v>
@@ -14635,7 +14635,7 @@
         <v>0.29</v>
       </c>
       <c r="O212" t="n">
-        <v>0.7625000000000001</v>
+        <v>0.7625</v>
       </c>
       <c r="P212" t="n">
         <v>3</v>
@@ -14836,7 +14836,7 @@
         <v>0.29</v>
       </c>
       <c r="O215" t="n">
-        <v>0.7300000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="P215" t="n">
         <v>1</v>
@@ -14903,7 +14903,7 @@
         <v>0.5</v>
       </c>
       <c r="O216" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -15037,7 +15037,7 @@
         <v>0.22</v>
       </c>
       <c r="O218" t="n">
-        <v>0.7380000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="P218" t="n">
         <v>2</v>
@@ -15104,7 +15104,7 @@
         <v>0.35</v>
       </c>
       <c r="O219" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="P219" t="n">
         <v>3</v>
@@ -15238,7 +15238,7 @@
         <v>0.22</v>
       </c>
       <c r="O221" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="P221" t="n">
         <v>1</v>
@@ -15372,7 +15372,7 @@
         <v>0.46</v>
       </c>
       <c r="O223" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="P223" t="n">
         <v>3</v>
@@ -15439,7 +15439,7 @@
         <v>0.22</v>
       </c>
       <c r="O224" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="P224" t="n">
         <v>1</v>
@@ -15640,7 +15640,7 @@
         <v>0.22</v>
       </c>
       <c r="O227" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="P227" t="n">
         <v>1</v>
@@ -15774,7 +15774,7 @@
         <v>0.46</v>
       </c>
       <c r="O229" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="P229" t="n">
         <v>3</v>
@@ -16042,7 +16042,7 @@
         <v>0.15</v>
       </c>
       <c r="O233" t="n">
-        <v>0.6329999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -16243,7 +16243,7 @@
         <v>0.29</v>
       </c>
       <c r="O236" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="P236" t="n">
         <v>3</v>
@@ -16377,7 +16377,7 @@
         <v>0.85</v>
       </c>
       <c r="O238" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="P238" t="n">
         <v>2</v>
@@ -16444,7 +16444,7 @@
         <v>0.15</v>
       </c>
       <c r="O239" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
@@ -16511,7 +16511,7 @@
         <v>0.46</v>
       </c>
       <c r="O240" t="n">
-        <v>0.6379999999999999</v>
+        <v>0.638</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
@@ -16578,7 +16578,7 @@
         <v>0.67</v>
       </c>
       <c r="O241" t="n">
-        <v>0.4985000000000001</v>
+        <v>0.4985</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>

--- a/Ground Truth/ground_truth_shower.xlsx
+++ b/Ground Truth/ground_truth_shower.xlsx
@@ -571,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7164929405168461</v>
+        <v>0.6746975189866966</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1361336586982008</v>
+        <v>0.1281925286074724</v>
       </c>
       <c r="S2" t="n">
         <v>4.5</v>
@@ -638,10 +638,10 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.19415490086141</v>
+        <v>1.124495864977828</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268894311636679</v>
+        <v>0.2136542143457873</v>
       </c>
       <c r="S3" t="n">
         <v>7.5</v>
@@ -687,7 +687,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="L4" t="n">
         <v>0.85</v>
@@ -699,16 +699,16 @@
         <v>0.76</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7875</v>
+        <v>0.7845</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.910647841378256</v>
+        <v>1.799193383964524</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3630230898618687</v>
+        <v>0.3418467429532597</v>
       </c>
       <c r="S4" t="n">
         <v>12</v>
@@ -772,10 +772,10 @@
         <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6368826137927519</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
@@ -839,10 +839,10 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.114544574137316</v>
+        <v>1.02538100820633</v>
       </c>
       <c r="R6" t="n">
-        <v>0.21176346908609</v>
+        <v>0.1948223915592028</v>
       </c>
       <c r="S6" t="n">
         <v>10.5</v>
@@ -906,10 +906,10 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274325</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -973,10 +973,10 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.19415490086141</v>
+        <v>1.124495864977828</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268894311636679</v>
+        <v>0.2136542143457873</v>
       </c>
       <c r="S8" t="n">
         <v>7.5</v>
@@ -1022,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="L9" t="n">
         <v>0.85</v>
@@ -1034,16 +1034,16 @@
         <v>0.76</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8195</v>
+        <v>0.8165</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.910647841378256</v>
+        <v>1.799193383964524</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3630230898618687</v>
+        <v>0.3418467429532597</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
@@ -1089,7 +1089,7 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L10" t="n">
         <v>0.6899999999999999</v>
@@ -1101,16 +1101,16 @@
         <v>0.93</v>
       </c>
       <c r="O10" t="n">
-        <v>0.751</v>
+        <v>0.748</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.865971762067384</v>
+        <v>2.698790075946786</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5445346347928031</v>
+        <v>0.5127701144298894</v>
       </c>
       <c r="S10" t="n">
         <v>18</v>
@@ -1174,10 +1174,10 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S11" t="n">
         <v>12.5</v>
@@ -1241,10 +1241,10 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85757429022886</v>
+        <v>1.708968347010551</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3529391151434834</v>
+        <v>0.3247039859320047</v>
       </c>
       <c r="S12" t="n">
         <v>17.5</v>
@@ -1308,10 +1308,10 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6536775574698</v>
+        <v>2.441383352872215</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5041987359192619</v>
+        <v>0.4638628370457208</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1375,10 +1375,10 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.79610326724094</v>
+        <v>0.7324150058616647</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1512596207757786</v>
+        <v>0.1391588511137163</v>
       </c>
       <c r="S14" t="n">
         <v>7.5</v>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.114544574137316</v>
+        <v>1.025381008206331</v>
       </c>
       <c r="R15" t="n">
-        <v>0.21176346908609</v>
+        <v>0.1948223915592029</v>
       </c>
       <c r="S15" t="n">
         <v>10.5</v>
@@ -1509,10 +1509,10 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -1558,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L17" t="n">
         <v>0.77</v>
@@ -1570,16 +1570,16 @@
         <v>0.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6995</v>
+        <v>0.6965</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38830980172282</v>
+        <v>2.248991729955655</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4273084286915745</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -1643,10 +1643,10 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.58246470258423</v>
+        <v>3.373487594933482</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6806682934910037</v>
+        <v>0.6409626430373616</v>
       </c>
       <c r="S18" t="n">
         <v>22.5</v>
@@ -1710,10 +1710,10 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.776619603445639</v>
+        <v>4.49798345991131</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9075577246546715</v>
+        <v>0.854616857383149</v>
       </c>
       <c r="S19" t="n">
         <v>30</v>
@@ -1777,10 +1777,10 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.19415490086141</v>
+        <v>1.124495864977828</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268894311636679</v>
+        <v>0.2136542143457873</v>
       </c>
       <c r="S20" t="n">
         <v>7.5</v>
@@ -1844,10 +1844,10 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.671816861205974</v>
+        <v>1.574294210968959</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3176452036291351</v>
+        <v>0.2991159000841022</v>
       </c>
       <c r="S21" t="n">
         <v>10.5</v>
@@ -1893,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L22" t="n">
         <v>0.77</v>
@@ -1905,16 +1905,16 @@
         <v>0.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.38830980172282</v>
+        <v>2.248991729955656</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4273084286915746</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -1978,10 +1978,10 @@
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7164929405168461</v>
+        <v>0.6746975189866966</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1361336586982008</v>
+        <v>0.1281925286074724</v>
       </c>
       <c r="S23" t="n">
         <v>4.5</v>
@@ -2045,10 +2045,10 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.432985881033692</v>
+        <v>1.349395037973393</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2722673173964015</v>
+        <v>0.2563850572149447</v>
       </c>
       <c r="S24" t="n">
         <v>9</v>
@@ -2112,10 +2112,10 @@
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.149478821550538</v>
+        <v>2.02409255696009</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4084009760946022</v>
+        <v>0.3845775858224171</v>
       </c>
       <c r="S25" t="n">
         <v>13.5</v>
@@ -2179,10 +2179,10 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S26" t="n">
         <v>12.5</v>
@@ -2246,10 +2246,10 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -2295,7 +2295,7 @@
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L28" t="n">
         <v>0.38</v>
@@ -2307,16 +2307,16 @@
         <v>0.67</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5445</v>
+        <v>0.5505</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S28" t="n">
         <v>30</v>
@@ -2380,10 +2380,10 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.458178296549263</v>
+        <v>4.198117895917224</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8470538763443599</v>
+        <v>0.7976424002242726</v>
       </c>
       <c r="S29" t="n">
         <v>28</v>
@@ -2447,10 +2447,10 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.687267444823894</v>
+        <v>6.297176843875836</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27058081451654</v>
+        <v>1.196463600336409</v>
       </c>
       <c r="S30" t="n">
         <v>42</v>
@@ -2514,10 +2514,10 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.916356593098525</v>
+        <v>8.396235791834448</v>
       </c>
       <c r="R31" t="n">
-        <v>1.69410775268872</v>
+        <v>1.595284800448545</v>
       </c>
       <c r="S31" t="n">
         <v>56</v>
@@ -2563,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="L32" t="n">
         <v>0.26</v>
@@ -2575,16 +2575,16 @@
         <v>0.57</v>
       </c>
       <c r="O32" t="n">
-        <v>0.4815</v>
+        <v>0.4875</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.71514858045772</v>
+        <v>3.417936694021102</v>
       </c>
       <c r="R32" t="n">
-        <v>0.7058782302869667</v>
+        <v>0.6494079718640094</v>
       </c>
       <c r="S32" t="n">
         <v>35</v>
@@ -2630,7 +2630,7 @@
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2642,16 +2642,16 @@
         <v>0.52</v>
       </c>
       <c r="O33" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.572722870686579</v>
+        <v>5.126905041031653</v>
       </c>
       <c r="R33" t="n">
-        <v>1.05881734543045</v>
+        <v>0.974111957796014</v>
       </c>
       <c r="S33" t="n">
         <v>52.5</v>
@@ -2715,10 +2715,10 @@
         <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.687267444823896</v>
+        <v>6.152286049237984</v>
       </c>
       <c r="R34" t="n">
-        <v>1.27058081451654</v>
+        <v>1.168934349355217</v>
       </c>
       <c r="S34" t="n">
         <v>63</v>
@@ -2764,7 +2764,7 @@
         <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L35" t="n">
         <v>0.77</v>
@@ -2776,16 +2776,16 @@
         <v>0.5</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6995</v>
+        <v>0.6965</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.38830980172282</v>
+        <v>2.248991729955655</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4273084286915745</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -2849,10 +2849,10 @@
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.980516336204699</v>
+        <v>3.748319549926092</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7562981038788928</v>
+        <v>0.7121807144859575</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -2898,7 +2898,7 @@
         <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0.19</v>
@@ -2910,16 +2910,16 @@
         <v>0.52</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2815</v>
+        <v>0.2785</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.970774504307049</v>
+        <v>5.622479324889138</v>
       </c>
       <c r="R37" t="n">
-        <v>1.134447155818339</v>
+        <v>1.068271071728936</v>
       </c>
       <c r="S37" t="n">
         <v>37.5</v>
@@ -2983,10 +2983,10 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -3050,10 +3050,10 @@
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.38830980172282</v>
+        <v>2.197245017584994</v>
       </c>
       <c r="R39" t="n">
-        <v>0.4537788623273358</v>
+        <v>0.4174765533411489</v>
       </c>
       <c r="S39" t="n">
         <v>22.5</v>
@@ -3099,7 +3099,7 @@
         <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L40" t="n">
         <v>0.38</v>
@@ -3111,16 +3111,16 @@
         <v>0.67</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R40" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S40" t="n">
         <v>30</v>
@@ -3184,10 +3184,10 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.343633722411948</v>
+        <v>3.148588421937917</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6352904072582701</v>
+        <v>0.5982318001682043</v>
       </c>
       <c r="S41" t="n">
         <v>21</v>
@@ -3251,10 +3251,10 @@
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.572722870686579</v>
+        <v>5.247647369896529</v>
       </c>
       <c r="R42" t="n">
-        <v>1.05881734543045</v>
+        <v>0.9970530002803405</v>
       </c>
       <c r="S42" t="n">
         <v>35</v>
@@ -3318,10 +3318,10 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>8.359084306029871</v>
+        <v>7.871471054844793</v>
       </c>
       <c r="R43" t="n">
-        <v>1.588226018145676</v>
+        <v>1.495579500420511</v>
       </c>
       <c r="S43" t="n">
         <v>52.5</v>
@@ -3385,10 +3385,10 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.600604006320404</v>
+        <v>2.392555685814771</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4941147612008768</v>
+        <v>0.4545855803048066</v>
       </c>
       <c r="S44" t="n">
         <v>24.5</v>
@@ -3434,7 +3434,7 @@
         <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="L45" t="n">
         <v>0.08</v>
@@ -3446,16 +3446,16 @@
         <v>0.67</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3995</v>
+        <v>0.4055</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.458178296549264</v>
+        <v>4.101524032825322</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7792895662368112</v>
       </c>
       <c r="S45" t="n">
         <v>42</v>
@@ -3501,7 +3501,7 @@
         <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3513,16 +3513,16 @@
         <v>0.48</v>
       </c>
       <c r="O46" t="n">
-        <v>0.239</v>
+        <v>0.245</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.944237728732352</v>
+        <v>5.468698710433763</v>
       </c>
       <c r="R46" t="n">
-        <v>1.129405168459147</v>
+        <v>1.039052754982415</v>
       </c>
       <c r="S46" t="n">
         <v>56</v>
@@ -3586,10 +3586,10 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.642591365513023</v>
+        <v>7.196773535858097</v>
       </c>
       <c r="R47" t="n">
-        <v>1.452092359447474</v>
+        <v>1.367386971813038</v>
       </c>
       <c r="S47" t="n">
         <v>48</v>
@@ -3653,10 +3653,10 @@
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.553239206891277</v>
+        <v>8.995966919822621</v>
       </c>
       <c r="R48" t="n">
-        <v>1.815115449309343</v>
+        <v>1.709233714766298</v>
       </c>
       <c r="S48" t="n">
         <v>60</v>
@@ -3720,10 +3720,10 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.46388704826953</v>
+        <v>10.79516030378715</v>
       </c>
       <c r="R49" t="n">
-        <v>2.178138539171211</v>
+        <v>2.051080457719558</v>
       </c>
       <c r="S49" t="n">
         <v>72</v>
@@ -3787,10 +3787,10 @@
         <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -3854,10 +3854,10 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S51" t="n">
         <v>16</v>
@@ -3921,10 +3921,10 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="S52" t="n">
         <v>24</v>
@@ -3970,7 +3970,7 @@
         <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="L53" t="n">
         <v>0.13</v>
@@ -3982,16 +3982,16 @@
         <v>0.57</v>
       </c>
       <c r="O53" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.245884091951679</v>
+        <v>3.906213364595545</v>
       </c>
       <c r="R53" t="n">
-        <v>0.8067179774708191</v>
+        <v>0.7421805392731535</v>
       </c>
       <c r="S53" t="n">
         <v>40</v>
@@ -4037,7 +4037,7 @@
         <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4049,16 +4049,16 @@
         <v>0.57</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2145</v>
+        <v>0.2205</v>
       </c>
       <c r="P54" t="n">
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.944237728732352</v>
+        <v>5.468698710433763</v>
       </c>
       <c r="R54" t="n">
-        <v>1.129405168459147</v>
+        <v>1.039052754982415</v>
       </c>
       <c r="S54" t="n">
         <v>56</v>
@@ -4122,10 +4122,10 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>7.642591365513023</v>
+        <v>7.031184056271981</v>
       </c>
       <c r="R55" t="n">
-        <v>1.452092359447474</v>
+        <v>1.335924970691676</v>
       </c>
       <c r="S55" t="n">
         <v>72</v>
@@ -4189,10 +4189,10 @@
         <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.6368826137927519</v>
+        <v>0.5997311279881747</v>
       </c>
       <c r="R56" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.1139489143177532</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -4256,10 +4256,10 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.955323920689128</v>
+        <v>0.8995966919822621</v>
       </c>
       <c r="R57" t="n">
-        <v>0.1815115449309343</v>
+        <v>0.1709233714766298</v>
       </c>
       <c r="S57" t="n">
         <v>6</v>
@@ -4323,10 +4323,10 @@
         <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R58" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.284872285794383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.79610326724094</v>
+        <v>0.7324150058616647</v>
       </c>
       <c r="R59" t="n">
-        <v>0.1512596207757786</v>
+        <v>0.1391588511137163</v>
       </c>
       <c r="S59" t="n">
         <v>7.5</v>
@@ -4457,10 +4457,10 @@
         <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R60" t="n">
-        <v>0.252099367959631</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S60" t="n">
         <v>12.5</v>
@@ -4524,10 +4524,10 @@
         <v>3</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4033589887354097</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -4591,10 +4591,10 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.821295682756512</v>
+        <v>3.598386767929048</v>
       </c>
       <c r="R62" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.6836934859065192</v>
       </c>
       <c r="S62" t="n">
         <v>24</v>
@@ -4658,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.731943524134769</v>
+        <v>5.397580151893573</v>
       </c>
       <c r="R63" t="n">
-        <v>1.089069269585606</v>
+        <v>1.025540228859779</v>
       </c>
       <c r="S63" t="n">
         <v>36</v>
@@ -4725,10 +4725,10 @@
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>7.16492940516846</v>
+        <v>6.746975189866965</v>
       </c>
       <c r="R64" t="n">
-        <v>1.361336586982007</v>
+        <v>1.281925286074723</v>
       </c>
       <c r="S64" t="n">
         <v>45</v>
@@ -4792,10 +4792,10 @@
         <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R65" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -4859,10 +4859,10 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R66" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S66" t="n">
         <v>16</v>
@@ -4926,10 +4926,10 @@
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="R67" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="S67" t="n">
         <v>24</v>
@@ -4993,10 +4993,10 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.78636143534329</v>
+        <v>2.623823684948265</v>
       </c>
       <c r="R68" t="n">
-        <v>0.5294086727152251</v>
+        <v>0.4985265001401702</v>
       </c>
       <c r="S68" t="n">
         <v>17.5</v>
@@ -5060,10 +5060,10 @@
         <v>2</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.458178296549264</v>
+        <v>4.198117895917223</v>
       </c>
       <c r="R69" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7976424002242724</v>
       </c>
       <c r="S69" t="n">
         <v>28</v>
@@ -5127,10 +5127,10 @@
         <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.687267444823896</v>
+        <v>6.297176843875834</v>
       </c>
       <c r="R70" t="n">
-        <v>1.27058081451654</v>
+        <v>1.196463600336409</v>
       </c>
       <c r="S70" t="n">
         <v>42</v>
@@ -5194,10 +5194,10 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.572458236379779</v>
+        <v>1.452277499742181</v>
       </c>
       <c r="R71" t="n">
-        <v>0.298767064912158</v>
+        <v>0.2759327249510145</v>
       </c>
       <c r="S71" t="n">
         <v>14</v>
@@ -5261,10 +5261,10 @@
         <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.751801913664612</v>
+        <v>2.541485624548817</v>
       </c>
       <c r="R72" t="n">
-        <v>0.5228423635962763</v>
+        <v>0.4828822686642753</v>
       </c>
       <c r="S72" t="n">
         <v>24.5</v>
@@ -5310,7 +5310,7 @@
         <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="L73" t="n">
         <v>0.26</v>
@@ -5322,16 +5322,16 @@
         <v>0.57</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4875</v>
+        <v>0.4905</v>
       </c>
       <c r="P73" t="n">
         <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.931145590949447</v>
+        <v>3.630693749355454</v>
       </c>
       <c r="R73" t="n">
-        <v>0.7469176622803949</v>
+        <v>0.6898318123775362</v>
       </c>
       <c r="S73" t="n">
         <v>35</v>
@@ -5395,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.093319598822689</v>
+        <v>1.951526818449605</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3977307237763109</v>
+        <v>0.3707900955054249</v>
       </c>
       <c r="S74" t="n">
         <v>16</v>
@@ -5444,7 +5444,7 @@
         <v>7</v>
       </c>
       <c r="K75" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="L75" t="n">
         <v>0.44</v>
@@ -5456,16 +5456,16 @@
         <v>0.31</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="P75" t="n">
         <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.663309297939705</v>
+        <v>3.415171932286808</v>
       </c>
       <c r="R75" t="n">
-        <v>0.696028766608544</v>
+        <v>0.6488826671344936</v>
       </c>
       <c r="S75" t="n">
         <v>28</v>
@@ -5529,10 +5529,10 @@
         <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.233298997056721</v>
+        <v>4.878817046124012</v>
       </c>
       <c r="R76" t="n">
-        <v>0.994326809440777</v>
+        <v>0.9269752387635622</v>
       </c>
       <c r="S76" t="n">
         <v>40</v>
@@ -5578,7 +5578,7 @@
         <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
@@ -5590,16 +5590,16 @@
         <v>0.22</v>
       </c>
       <c r="O77" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.7627780141936447</v>
+        <v>0.7099389740842112</v>
       </c>
       <c r="R77" t="n">
-        <v>0.1449278226967925</v>
+        <v>0.1348884050760001</v>
       </c>
       <c r="S77" t="n">
         <v>6</v>
@@ -5645,7 +5645,7 @@
         <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L78" t="n">
         <v>0.74</v>
@@ -5657,16 +5657,16 @@
         <v>0.46</v>
       </c>
       <c r="O78" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="P78" t="n">
         <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.034074704516386</v>
+        <v>1.893170597557897</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3864741938581134</v>
+        <v>0.3597024135360004</v>
       </c>
       <c r="S78" t="n">
         <v>16</v>
@@ -5730,10 +5730,10 @@
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421056</v>
       </c>
       <c r="R79" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800006</v>
       </c>
       <c r="S79" t="n">
         <v>30</v>
@@ -5779,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L80" t="n">
         <v>0.9</v>
@@ -5791,16 +5791,16 @@
         <v>0.29</v>
       </c>
       <c r="O80" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7585</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.18489788612605</v>
+        <v>1.098128801339945</v>
       </c>
       <c r="R80" t="n">
-        <v>0.2251305983639495</v>
+        <v>0.2086444722545895</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -5864,10 +5864,10 @@
         <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.962244715315125</v>
+        <v>2.745322003349862</v>
       </c>
       <c r="R81" t="n">
-        <v>0.5628264959098738</v>
+        <v>0.5216111806364737</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -5913,7 +5913,7 @@
         <v>18</v>
       </c>
       <c r="K82" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -5925,16 +5925,16 @@
         <v>0.4</v>
       </c>
       <c r="O82" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.332040487567225</v>
+        <v>4.941579606029751</v>
       </c>
       <c r="R82" t="n">
-        <v>1.013087692637773</v>
+        <v>0.9389001251456527</v>
       </c>
       <c r="S82" t="n">
         <v>45</v>
@@ -5998,10 +5998,10 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.370038180833246</v>
+        <v>1.280491991626532</v>
       </c>
       <c r="R83" t="n">
-        <v>0.2603072543583166</v>
+        <v>0.2432934784090411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.288091633999789</v>
+        <v>3.073180779903677</v>
       </c>
       <c r="R84" t="n">
-        <v>0.62473741045996</v>
+        <v>0.5839043481816986</v>
       </c>
       <c r="S84" t="n">
         <v>24</v>
@@ -6132,10 +6132,10 @@
         <v>3</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.480152723332982</v>
+        <v>5.121967966506128</v>
       </c>
       <c r="R85" t="n">
-        <v>1.041229017433267</v>
+        <v>0.9731739136361643</v>
       </c>
       <c r="S85" t="n">
         <v>40</v>
@@ -6199,10 +6199,10 @@
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.7467325219856878</v>
+        <v>0.7010337259087951</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1418791791772807</v>
+        <v>0.1331964079226711</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -6266,10 +6266,10 @@
         <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.613563826949908</v>
+        <v>2.453618040680783</v>
       </c>
       <c r="R87" t="n">
-        <v>0.4965771271204825</v>
+        <v>0.4661874277293487</v>
       </c>
       <c r="S87" t="n">
         <v>17.5</v>
@@ -6333,10 +6333,10 @@
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.227127653899815</v>
+        <v>4.907236081361566</v>
       </c>
       <c r="R88" t="n">
-        <v>0.9931542542409649</v>
+        <v>0.9323748554586975</v>
       </c>
       <c r="S88" t="n">
         <v>35</v>
@@ -6400,10 +6400,10 @@
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.318198898315231</v>
+        <v>1.215631175047444</v>
       </c>
       <c r="R89" t="n">
-        <v>0.2504577906798938</v>
+        <v>0.2309699232590144</v>
       </c>
       <c r="S89" t="n">
         <v>12</v>
@@ -6449,7 +6449,7 @@
         <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="L90" t="n">
         <v>0.64</v>
@@ -6461,16 +6461,16 @@
         <v>0.57</v>
       </c>
       <c r="O90" t="n">
-        <v>0.7175</v>
+        <v>0.7205</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.196998163858717</v>
+        <v>2.026051958412407</v>
       </c>
       <c r="R90" t="n">
-        <v>0.4174296511331563</v>
+        <v>0.3849498720983573</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -6516,7 +6516,7 @@
         <v>16</v>
       </c>
       <c r="K91" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L91" t="n">
         <v>0.33</v>
@@ -6528,16 +6528,16 @@
         <v>0.48</v>
       </c>
       <c r="O91" t="n">
-        <v>0.4925</v>
+        <v>0.4955</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.515197062173948</v>
+        <v>3.241683133459851</v>
       </c>
       <c r="R91" t="n">
-        <v>0.6678874418130502</v>
+        <v>0.6159197953573717</v>
       </c>
       <c r="S91" t="n">
         <v>32</v>
@@ -6601,10 +6601,10 @@
         <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.345352808205619</v>
+        <v>1.25617689958832</v>
       </c>
       <c r="R92" t="n">
-        <v>0.2556170335590677</v>
+        <v>0.2386736109217809</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -6668,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.152564493128991</v>
+        <v>2.009883039341312</v>
       </c>
       <c r="R93" t="n">
-        <v>0.4089872536945083</v>
+        <v>0.3818777774748494</v>
       </c>
       <c r="S93" t="n">
         <v>16</v>
@@ -6735,10 +6735,10 @@
         <v>3</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.228846739693486</v>
+        <v>3.014824559011969</v>
       </c>
       <c r="R94" t="n">
-        <v>0.6134808805417624</v>
+        <v>0.572816666212274</v>
       </c>
       <c r="S94" t="n">
         <v>24</v>
@@ -6802,10 +6802,10 @@
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.789689515502888</v>
+        <v>1.676599652152576</v>
       </c>
       <c r="R95" t="n">
-        <v>0.3400410079455487</v>
+        <v>0.3185539339089895</v>
       </c>
       <c r="S95" t="n">
         <v>12.5</v>
@@ -6869,10 +6869,10 @@
         <v>2</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.863503224804621</v>
+        <v>2.682559443444122</v>
       </c>
       <c r="R96" t="n">
-        <v>0.544065612712878</v>
+        <v>0.5096862942543832</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -6936,10 +6936,10 @@
         <v>3</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.295254837206931</v>
+        <v>4.023839165166183</v>
       </c>
       <c r="R97" t="n">
-        <v>0.8160984190693169</v>
+        <v>0.7645294413815747</v>
       </c>
       <c r="S97" t="n">
         <v>30</v>
@@ -7003,10 +7003,10 @@
         <v>2</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.246611317695115</v>
+        <v>1.158916531435473</v>
       </c>
       <c r="R98" t="n">
-        <v>0.2368561503620719</v>
+        <v>0.22019414097274</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -7070,10 +7070,10 @@
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.994578108312184</v>
+        <v>1.854266450296758</v>
       </c>
       <c r="R99" t="n">
-        <v>0.378969840579315</v>
+        <v>0.352310625556384</v>
       </c>
       <c r="S99" t="n">
         <v>16</v>
@@ -7119,7 +7119,7 @@
         <v>12</v>
       </c>
       <c r="K100" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="L100" t="n">
         <v>0.54</v>
@@ -7131,16 +7131,16 @@
         <v>0.67</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6165</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.991867162468276</v>
+        <v>2.781399675445137</v>
       </c>
       <c r="R100" t="n">
-        <v>0.5684547608689725</v>
+        <v>0.528465938334576</v>
       </c>
       <c r="S100" t="n">
         <v>24</v>
@@ -7204,10 +7204,10 @@
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.635405936580226</v>
+        <v>1.524630326913753</v>
       </c>
       <c r="R101" t="n">
-        <v>0.3107271279502429</v>
+        <v>0.2896797621136131</v>
       </c>
       <c r="S101" t="n">
         <v>12.5</v>
@@ -7253,7 +7253,7 @@
         <v>8</v>
       </c>
       <c r="K102" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L102" t="n">
         <v>0.64</v>
@@ -7265,16 +7265,16 @@
         <v>0.76</v>
       </c>
       <c r="O102" t="n">
-        <v>0.712</v>
+        <v>0.715</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R102" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -7320,7 +7320,7 @@
         <v>12</v>
       </c>
       <c r="K103" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="L103" t="n">
         <v>0.38</v>
@@ -7332,16 +7332,16 @@
         <v>0.67</v>
       </c>
       <c r="O103" t="n">
-        <v>0.5385</v>
+        <v>0.5415</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.924974247792541</v>
+        <v>3.659112784593008</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7457451070805828</v>
+        <v>0.6952314290726715</v>
       </c>
       <c r="S103" t="n">
         <v>30</v>
@@ -7405,10 +7405,10 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="R104" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="S104" t="n">
         <v>12.5</v>
@@ -7463,19 +7463,19 @@
         <v>0.89</v>
       </c>
       <c r="N105" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="O105" t="n">
-        <v>0.654</v>
+        <v>0.699</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R105" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -7539,10 +7539,10 @@
         <v>3</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.184170660382614</v>
+        <v>3.914421250994231</v>
       </c>
       <c r="R106" t="n">
-        <v>0.7949924254726968</v>
+        <v>0.743740037688904</v>
       </c>
       <c r="S106" t="n">
         <v>30</v>
@@ -7588,7 +7588,7 @@
         <v>8</v>
       </c>
       <c r="K107" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L107" t="n">
         <v>0.64</v>
@@ -7600,16 +7600,16 @@
         <v>0.46</v>
       </c>
       <c r="O107" t="n">
-        <v>0.667</v>
+        <v>0.67</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R107" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -7673,10 +7673,10 @@
         <v>2</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.270811873160451</v>
+        <v>3.049260653827508</v>
       </c>
       <c r="R108" t="n">
-        <v>0.6214542559004858</v>
+        <v>0.5793595242272265</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -7722,7 +7722,7 @@
         <v>12</v>
       </c>
       <c r="K109" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="L109" t="n">
         <v>0.38</v>
@@ -7734,16 +7734,16 @@
         <v>0.67</v>
       </c>
       <c r="O109" t="n">
-        <v>0.5185</v>
+        <v>0.5215</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.924974247792541</v>
+        <v>3.659112784593009</v>
       </c>
       <c r="R109" t="n">
-        <v>0.7457451070805828</v>
+        <v>0.6952314290726717</v>
       </c>
       <c r="S109" t="n">
         <v>30</v>
@@ -7807,10 +7807,10 @@
         <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.288091633999789</v>
+        <v>3.073180779903677</v>
       </c>
       <c r="R110" t="n">
-        <v>0.62473741045996</v>
+        <v>0.5839043481816986</v>
       </c>
       <c r="S110" t="n">
         <v>24</v>
@@ -7874,10 +7874,10 @@
         <v>2</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.110114542499736</v>
+        <v>3.841475974879596</v>
       </c>
       <c r="R111" t="n">
-        <v>0.7809217630749499</v>
+        <v>0.7298804352271232</v>
       </c>
       <c r="S111" t="n">
         <v>30</v>
@@ -7923,7 +7923,7 @@
         <v>12</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="L112" t="n">
         <v>0.23</v>
@@ -7935,16 +7935,16 @@
         <v>0.67</v>
       </c>
       <c r="O112" t="n">
-        <v>0.413</v>
+        <v>0.416</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.932137450999684</v>
+        <v>4.609771169855515</v>
       </c>
       <c r="R112" t="n">
-        <v>0.93710611568994</v>
+        <v>0.8758565222725478</v>
       </c>
       <c r="S112" t="n">
         <v>36</v>
@@ -8008,10 +8008,10 @@
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.49322263539023</v>
+        <v>2.317833062870947</v>
       </c>
       <c r="R113" t="n">
-        <v>0.4737123007241438</v>
+        <v>0.44038828194548</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -8075,10 +8075,10 @@
         <v>2</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.116528294237788</v>
+        <v>2.897291328588684</v>
       </c>
       <c r="R114" t="n">
-        <v>0.5921403759051797</v>
+        <v>0.55048535243185</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -8124,7 +8124,7 @@
         <v>12</v>
       </c>
       <c r="K115" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="L115" t="n">
         <v>0.38</v>
@@ -8136,16 +8136,16 @@
         <v>0.67</v>
       </c>
       <c r="O115" t="n">
-        <v>0.5265</v>
+        <v>0.5295</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.739833953085346</v>
+        <v>3.476749594306421</v>
       </c>
       <c r="R115" t="n">
-        <v>0.7105684510862157</v>
+        <v>0.66058242291822</v>
       </c>
       <c r="S115" t="n">
         <v>30</v>
@@ -8209,10 +8209,10 @@
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.093319598822689</v>
+        <v>1.951526818449605</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3977307237763109</v>
+        <v>0.3707900955054249</v>
       </c>
       <c r="S116" t="n">
         <v>16</v>
@@ -8258,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="K117" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L117" t="n">
         <v>0.64</v>
@@ -8270,16 +8270,16 @@
         <v>0.57</v>
       </c>
       <c r="O117" t="n">
-        <v>0.6955</v>
+        <v>0.6985</v>
       </c>
       <c r="P117" t="n">
         <v>2</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R117" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S117" t="n">
         <v>20</v>
@@ -8325,7 +8325,7 @@
         <v>12</v>
       </c>
       <c r="K118" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="L118" t="n">
         <v>0.54</v>
@@ -8337,16 +8337,16 @@
         <v>0.67</v>
       </c>
       <c r="O118" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.139979398234034</v>
+        <v>2.927290227674407</v>
       </c>
       <c r="R118" t="n">
-        <v>0.5965960856644664</v>
+        <v>0.5561851432581373</v>
       </c>
       <c r="S118" t="n">
         <v>24</v>
@@ -8410,10 +8410,10 @@
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>2.542593380645482</v>
+        <v>2.366463246947371</v>
       </c>
       <c r="R119" t="n">
-        <v>0.4830927423226417</v>
+        <v>0.4496280169200005</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -8477,10 +8477,10 @@
         <v>2</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.178241725806853</v>
+        <v>2.958079058684214</v>
       </c>
       <c r="R120" t="n">
-        <v>0.6038659279033021</v>
+        <v>0.5620350211500006</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -8544,10 +8544,10 @@
         <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421056</v>
       </c>
       <c r="R121" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800006</v>
       </c>
       <c r="S121" t="n">
         <v>30</v>
@@ -8611,10 +8611,10 @@
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.99025816810235</v>
+        <v>1.874159774963046</v>
       </c>
       <c r="R122" t="n">
-        <v>0.3781490519394464</v>
+        <v>0.3560903572429788</v>
       </c>
       <c r="S122" t="n">
         <v>12.5</v>
@@ -8678,10 +8678,10 @@
         <v>2</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.18441306896376</v>
+        <v>2.998655639940873</v>
       </c>
       <c r="R123" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.569744571588766</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -8745,10 +8745,10 @@
         <v>3</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.776619603445639</v>
+        <v>4.49798345991131</v>
       </c>
       <c r="R124" t="n">
-        <v>0.9075577246546715</v>
+        <v>0.854616857383149</v>
       </c>
       <c r="S124" t="n">
         <v>30</v>
@@ -8812,10 +8812,10 @@
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R125" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -8861,7 +8861,7 @@
         <v>8</v>
       </c>
       <c r="K126" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L126" t="n">
         <v>0.74</v>
@@ -8873,16 +8873,16 @@
         <v>0.76</v>
       </c>
       <c r="O126" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="P126" t="n">
         <v>2</v>
       </c>
       <c r="Q126" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="R126" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="S126" t="n">
         <v>16</v>
@@ -8946,10 +8946,10 @@
         <v>3</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.821295682756512</v>
+        <v>3.598386767929049</v>
       </c>
       <c r="R127" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.6836934859065193</v>
       </c>
       <c r="S127" t="n">
         <v>24</v>
@@ -9013,10 +9013,10 @@
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>1.99025816810235</v>
+        <v>1.874159774963046</v>
       </c>
       <c r="R128" t="n">
-        <v>0.3781490519394464</v>
+        <v>0.3560903572429788</v>
       </c>
       <c r="S128" t="n">
         <v>12.5</v>
@@ -9080,10 +9080,10 @@
         <v>2</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.18441306896376</v>
+        <v>2.998655639940873</v>
       </c>
       <c r="R129" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.569744571588766</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -9147,10 +9147,10 @@
         <v>3</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.776619603445639</v>
+        <v>4.49798345991131</v>
       </c>
       <c r="R130" t="n">
-        <v>0.9075577246546715</v>
+        <v>0.854616857383149</v>
       </c>
       <c r="S130" t="n">
         <v>30</v>
@@ -9214,10 +9214,10 @@
         <v>2</v>
       </c>
       <c r="Q131" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R131" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -9281,10 +9281,10 @@
         <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R132" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S132" t="n">
         <v>16</v>
@@ -9348,10 +9348,10 @@
         <v>3</v>
       </c>
       <c r="Q133" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="R133" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="S133" t="n">
         <v>24</v>
@@ -9415,10 +9415,10 @@
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R134" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S134" t="n">
         <v>12.5</v>
@@ -9482,10 +9482,10 @@
         <v>2</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R135" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -9531,7 +9531,7 @@
         <v>12</v>
       </c>
       <c r="K136" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L136" t="n">
         <v>0.38</v>
@@ -9543,16 +9543,16 @@
         <v>0.67</v>
       </c>
       <c r="O136" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="P136" t="n">
         <v>3</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S136" t="n">
         <v>30</v>
@@ -9598,7 +9598,7 @@
         <v>4</v>
       </c>
       <c r="K137" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="L137" t="n">
         <v>0.85</v>
@@ -9610,16 +9610,16 @@
         <v>0.29</v>
       </c>
       <c r="O137" t="n">
-        <v>0.702</v>
+        <v>0.699</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>1.7625356056125</v>
+        <v>1.653302831735254</v>
       </c>
       <c r="R137" t="n">
-        <v>0.334881765066375</v>
+        <v>0.3141275380296983</v>
       </c>
       <c r="S137" t="n">
         <v>12</v>
@@ -9683,10 +9683,10 @@
         <v>2</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.084437309821875</v>
+        <v>2.893279955536695</v>
       </c>
       <c r="R138" t="n">
-        <v>0.5860430888661562</v>
+        <v>0.5497231915519721</v>
       </c>
       <c r="S138" t="n">
         <v>21</v>
@@ -9750,10 +9750,10 @@
         <v>3</v>
       </c>
       <c r="Q139" t="n">
-        <v>4.406339014031249</v>
+        <v>4.133257079338136</v>
       </c>
       <c r="R139" t="n">
-        <v>0.8372044126659374</v>
+        <v>0.7853188450742458</v>
       </c>
       <c r="S139" t="n">
         <v>30</v>
@@ -9817,10 +9817,10 @@
         <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>2.429040666558403</v>
+        <v>2.282212070169283</v>
       </c>
       <c r="R140" t="n">
-        <v>0.4615177266460965</v>
+        <v>0.4336202933321637</v>
       </c>
       <c r="S140" t="n">
         <v>16</v>
@@ -9884,10 +9884,10 @@
         <v>2</v>
       </c>
       <c r="Q141" t="n">
-        <v>4.250821166477206</v>
+        <v>3.993871122796245</v>
       </c>
       <c r="R141" t="n">
-        <v>0.8076560216306691</v>
+        <v>0.7588355133312866</v>
       </c>
       <c r="S141" t="n">
         <v>28</v>
@@ -9951,10 +9951,10 @@
         <v>3</v>
       </c>
       <c r="Q142" t="n">
-        <v>6.072601666396007</v>
+        <v>5.705530175423207</v>
       </c>
       <c r="R142" t="n">
-        <v>1.153794316615241</v>
+        <v>1.084050733330409</v>
       </c>
       <c r="S142" t="n">
         <v>40</v>
@@ -10018,10 +10018,10 @@
         <v>2</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.2616649498528361</v>
+        <v>0.2439408523062006</v>
       </c>
       <c r="R143" t="n">
-        <v>0.04971634047203886</v>
+        <v>0.04634876193817811</v>
       </c>
       <c r="S143" t="n">
         <v>2</v>
@@ -10085,10 +10085,10 @@
         <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>1.569989699117017</v>
+        <v>1.463645113837203</v>
       </c>
       <c r="R144" t="n">
-        <v>0.2982980428322332</v>
+        <v>0.2780925716290686</v>
       </c>
       <c r="S144" t="n">
         <v>12</v>
@@ -10134,7 +10134,7 @@
         <v>12</v>
       </c>
       <c r="K145" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="L145" t="n">
         <v>0.54</v>
@@ -10146,16 +10146,16 @@
         <v>0.67</v>
       </c>
       <c r="O145" t="n">
-        <v>0.6395</v>
+        <v>0.6425</v>
       </c>
       <c r="P145" t="n">
         <v>3</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.139979398234034</v>
+        <v>2.927290227674407</v>
       </c>
       <c r="R145" t="n">
-        <v>0.5965960856644664</v>
+        <v>0.5561851432581373</v>
       </c>
       <c r="S145" t="n">
         <v>24</v>
@@ -10201,7 +10201,7 @@
         <v>7</v>
       </c>
       <c r="K146" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="L146" t="n">
         <v>0.71</v>
@@ -10213,16 +10213,16 @@
         <v>0.64</v>
       </c>
       <c r="O146" t="n">
-        <v>0.7375</v>
+        <v>0.7405</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
       </c>
       <c r="Q146" t="n">
-        <v>2.138370403868106</v>
+        <v>1.985552518945208</v>
       </c>
       <c r="R146" t="n">
-        <v>0.4062903767349402</v>
+        <v>0.3772549785995896</v>
       </c>
       <c r="S146" t="n">
         <v>17.5</v>
@@ -10268,7 +10268,7 @@
         <v>14</v>
       </c>
       <c r="K147" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="L147" t="n">
         <v>0.26</v>
@@ -10280,16 +10280,16 @@
         <v>0.57</v>
       </c>
       <c r="O147" t="n">
-        <v>0.4515</v>
+        <v>0.4545</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.276740807736212</v>
+        <v>3.971105037890417</v>
       </c>
       <c r="R147" t="n">
-        <v>0.8125807534698803</v>
+        <v>0.7545099571991791</v>
       </c>
       <c r="S147" t="n">
         <v>35</v>
@@ -10353,10 +10353,10 @@
         <v>3</v>
       </c>
       <c r="Q148" t="n">
-        <v>6.720592697871191</v>
+        <v>6.24030791668494</v>
       </c>
       <c r="R148" t="n">
-        <v>1.276912612595526</v>
+        <v>1.185658504170139</v>
       </c>
       <c r="S148" t="n">
         <v>55</v>
@@ -10420,10 +10420,10 @@
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>1.370038180833246</v>
+        <v>1.280491991626532</v>
       </c>
       <c r="R149" t="n">
-        <v>0.2603072543583166</v>
+        <v>0.2432934784090411</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -10487,10 +10487,10 @@
         <v>2</v>
       </c>
       <c r="Q150" t="n">
-        <v>2.192061089333193</v>
+        <v>2.048787186602451</v>
       </c>
       <c r="R150" t="n">
-        <v>0.4164916069733066</v>
+        <v>0.3892695654544657</v>
       </c>
       <c r="S150" t="n">
         <v>16</v>
@@ -10554,10 +10554,10 @@
         <v>3</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.288091633999789</v>
+        <v>3.073180779903677</v>
       </c>
       <c r="R151" t="n">
-        <v>0.62473741045996</v>
+        <v>0.5839043481816986</v>
       </c>
       <c r="S151" t="n">
         <v>24</v>
@@ -10621,10 +10621,10 @@
         <v>1</v>
       </c>
       <c r="Q152" t="n">
-        <v>1.589120862903426</v>
+        <v>1.479039529342106</v>
       </c>
       <c r="R152" t="n">
-        <v>0.301932963951651</v>
+        <v>0.2810175105750002</v>
       </c>
       <c r="S152" t="n">
         <v>12.5</v>
@@ -10688,10 +10688,10 @@
         <v>2</v>
       </c>
       <c r="Q153" t="n">
-        <v>2.542593380645482</v>
+        <v>2.36646324694737</v>
       </c>
       <c r="R153" t="n">
-        <v>0.4830927423226417</v>
+        <v>0.4496280169200003</v>
       </c>
       <c r="S153" t="n">
         <v>20</v>
@@ -10755,10 +10755,10 @@
         <v>3</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421055</v>
       </c>
       <c r="R154" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800005</v>
       </c>
       <c r="S154" t="n">
         <v>30</v>
@@ -10822,10 +10822,10 @@
         <v>1</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.962487123896271</v>
+        <v>1.829556392296504</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3728725535402914</v>
+        <v>0.3476157145363358</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -10871,7 +10871,7 @@
         <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L156" t="n">
         <v>0.64</v>
@@ -10883,16 +10883,16 @@
         <v>0.46</v>
       </c>
       <c r="O156" t="n">
-        <v>0.667</v>
+        <v>0.67</v>
       </c>
       <c r="P156" t="n">
         <v>2</v>
       </c>
       <c r="Q156" t="n">
-        <v>2.616649498528361</v>
+        <v>2.439408523062006</v>
       </c>
       <c r="R156" t="n">
-        <v>0.4971634047203885</v>
+        <v>0.4634876193817811</v>
       </c>
       <c r="S156" t="n">
         <v>20</v>
@@ -10956,10 +10956,10 @@
         <v>3</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.270811873160451</v>
+        <v>3.049260653827508</v>
       </c>
       <c r="R157" t="n">
-        <v>0.6214542559004858</v>
+        <v>0.5793595242272265</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -11023,10 +11023,10 @@
         <v>1</v>
       </c>
       <c r="Q158" t="n">
-        <v>2.542593380645482</v>
+        <v>2.366463246947371</v>
       </c>
       <c r="R158" t="n">
-        <v>0.4830927423226417</v>
+        <v>0.4496280169200005</v>
       </c>
       <c r="S158" t="n">
         <v>20</v>
@@ -11090,10 +11090,10 @@
         <v>2</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.178241725806853</v>
+        <v>2.958079058684214</v>
       </c>
       <c r="R159" t="n">
-        <v>0.6038659279033021</v>
+        <v>0.5620350211500006</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -11157,10 +11157,10 @@
         <v>3</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.813890070968224</v>
+        <v>3.549694870421056</v>
       </c>
       <c r="R160" t="n">
-        <v>0.7246391134839625</v>
+        <v>0.6744420253800006</v>
       </c>
       <c r="S160" t="n">
         <v>30</v>
@@ -11224,10 +11224,10 @@
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R161" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -11273,7 +11273,7 @@
         <v>8</v>
       </c>
       <c r="K162" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L162" t="n">
         <v>0.74</v>
@@ -11285,16 +11285,16 @@
         <v>0.76</v>
       </c>
       <c r="O162" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="P162" t="n">
         <v>2</v>
       </c>
       <c r="Q162" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="R162" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="S162" t="n">
         <v>16</v>
@@ -11358,10 +11358,10 @@
         <v>3</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.821295682756512</v>
+        <v>3.598386767929049</v>
       </c>
       <c r="R163" t="n">
-        <v>0.7260461797237373</v>
+        <v>0.6836934859065193</v>
       </c>
       <c r="S163" t="n">
         <v>24</v>
@@ -11425,10 +11425,10 @@
         <v>1</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R164" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S164" t="n">
         <v>12.5</v>
@@ -11492,10 +11492,10 @@
         <v>2</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R165" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S165" t="n">
         <v>20</v>
@@ -11541,7 +11541,7 @@
         <v>12</v>
       </c>
       <c r="K166" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="L166" t="n">
         <v>0.38</v>
@@ -11553,16 +11553,16 @@
         <v>0.67</v>
       </c>
       <c r="O166" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="P166" t="n">
         <v>3</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="R166" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="S166" t="n">
         <v>30</v>
@@ -11623,13 +11623,13 @@
         <v>0.785</v>
       </c>
       <c r="P167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q167" t="n">
-        <v>0.7109387316756299</v>
+        <v>0.6588772808039668</v>
       </c>
       <c r="R167" t="n">
-        <v>0.1350783590183697</v>
+        <v>0.1251866833527537</v>
       </c>
       <c r="S167" t="n">
         <v>6</v>
@@ -11675,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="K168" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L168" t="n">
         <v>0.9</v>
@@ -11687,16 +11687,16 @@
         <v>0.35</v>
       </c>
       <c r="O168" t="n">
-        <v>0.7825</v>
+        <v>0.7855</v>
       </c>
       <c r="P168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q168" t="n">
-        <v>1.18489788612605</v>
+        <v>1.098128801339945</v>
       </c>
       <c r="R168" t="n">
-        <v>0.2251305983639495</v>
+        <v>0.2086444722545895</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -11760,10 +11760,10 @@
         <v>1</v>
       </c>
       <c r="Q169" t="n">
-        <v>1.89583661780168</v>
+        <v>1.757006082143911</v>
       </c>
       <c r="R169" t="n">
-        <v>0.3602089573823192</v>
+        <v>0.3338311556073432</v>
       </c>
       <c r="S169" t="n">
         <v>16</v>
@@ -11827,10 +11827,10 @@
         <v>1</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.7961032672409399</v>
+        <v>0.7324150058616647</v>
       </c>
       <c r="R170" t="n">
-        <v>0.1512596207757786</v>
+        <v>0.1391588511137163</v>
       </c>
       <c r="S170" t="n">
         <v>7.5</v>
@@ -11894,10 +11894,10 @@
         <v>2</v>
       </c>
       <c r="Q171" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="R171" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="S171" t="n">
         <v>12.5</v>
@@ -11961,10 +11961,10 @@
         <v>3</v>
       </c>
       <c r="Q172" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="R172" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -12028,10 +12028,10 @@
         <v>1</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.8238743114470191</v>
+        <v>0.7597694844046526</v>
       </c>
       <c r="R173" t="n">
-        <v>0.1565361191749336</v>
+        <v>0.144356202036884</v>
       </c>
       <c r="S173" t="n">
         <v>7.5</v>
@@ -12095,10 +12095,10 @@
         <v>2</v>
       </c>
       <c r="Q174" t="n">
-        <v>1.373123852411698</v>
+        <v>1.266282474007754</v>
       </c>
       <c r="R174" t="n">
-        <v>0.2608935319582227</v>
+        <v>0.2405936700614733</v>
       </c>
       <c r="S174" t="n">
         <v>12.5</v>
@@ -12144,7 +12144,7 @@
         <v>8</v>
       </c>
       <c r="K175" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="L175" t="n">
         <v>0.64</v>
@@ -12156,16 +12156,16 @@
         <v>0.46</v>
       </c>
       <c r="O175" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="P175" t="n">
         <v>3</v>
       </c>
       <c r="Q175" t="n">
-        <v>2.196998163858717</v>
+        <v>2.026051958412407</v>
       </c>
       <c r="R175" t="n">
-        <v>0.4174296511331563</v>
+        <v>0.3849498720983573</v>
       </c>
       <c r="S175" t="n">
         <v>20</v>
@@ -12211,7 +12211,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -12223,16 +12223,16 @@
         <v>0.22</v>
       </c>
       <c r="O176" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="P176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.7627780141936447</v>
+        <v>0.7099389740842112</v>
       </c>
       <c r="R176" t="n">
-        <v>0.1449278226967925</v>
+        <v>0.1348884050760001</v>
       </c>
       <c r="S176" t="n">
         <v>6</v>
@@ -12296,10 +12296,10 @@
         <v>3</v>
       </c>
       <c r="Q177" t="n">
-        <v>1.271296690322741</v>
+        <v>1.183231623473685</v>
       </c>
       <c r="R177" t="n">
-        <v>0.2415463711613208</v>
+        <v>0.2248140084600002</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -12345,7 +12345,7 @@
         <v>8</v>
       </c>
       <c r="K178" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L178" t="n">
         <v>0.74</v>
@@ -12357,16 +12357,16 @@
         <v>0.76</v>
       </c>
       <c r="O178" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="P178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q178" t="n">
-        <v>2.034074704516386</v>
+        <v>1.893170597557897</v>
       </c>
       <c r="R178" t="n">
-        <v>0.3864741938581134</v>
+        <v>0.3597024135360004</v>
       </c>
       <c r="S178" t="n">
         <v>16</v>
@@ -12430,10 +12430,10 @@
         <v>3</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.9331070853242646</v>
+        <v>0.8777131091478717</v>
       </c>
       <c r="R179" t="n">
-        <v>0.1772903462116103</v>
+        <v>0.1667654907380956</v>
       </c>
       <c r="S179" t="n">
         <v>6</v>
@@ -12497,10 +12497,10 @@
         <v>2</v>
       </c>
       <c r="Q180" t="n">
-        <v>1.399660627986397</v>
+        <v>1.316569663721808</v>
       </c>
       <c r="R180" t="n">
-        <v>0.2659355193174154</v>
+        <v>0.2501482361071434</v>
       </c>
       <c r="S180" t="n">
         <v>9</v>
@@ -12546,7 +12546,7 @@
         <v>10</v>
       </c>
       <c r="K181" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L181" t="n">
         <v>0.77</v>
@@ -12558,16 +12558,16 @@
         <v>0.85</v>
       </c>
       <c r="O181" t="n">
-        <v>0.775</v>
+        <v>0.772</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
       </c>
       <c r="Q181" t="n">
-        <v>2.332767713310661</v>
+        <v>2.194282772869679</v>
       </c>
       <c r="R181" t="n">
-        <v>0.4432258655290257</v>
+        <v>0.416913726845239</v>
       </c>
       <c r="S181" t="n">
         <v>15</v>
@@ -12631,10 +12631,10 @@
         <v>1</v>
       </c>
       <c r="Q182" t="n">
-        <v>1.115778842768697</v>
+        <v>1.043845666931795</v>
       </c>
       <c r="R182" t="n">
-        <v>0.2119979801260525</v>
+        <v>0.198330676717041</v>
       </c>
       <c r="S182" t="n">
         <v>8</v>
@@ -12698,10 +12698,10 @@
         <v>2</v>
       </c>
       <c r="Q183" t="n">
-        <v>1.673668264153046</v>
+        <v>1.565768500397692</v>
       </c>
       <c r="R183" t="n">
-        <v>0.3179969701890787</v>
+        <v>0.2974960150755615</v>
       </c>
       <c r="S183" t="n">
         <v>12</v>
@@ -12765,10 +12765,10 @@
         <v>3</v>
       </c>
       <c r="Q184" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R184" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -12832,10 +12832,10 @@
         <v>1</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="R185" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="S185" t="n">
         <v>7.5</v>
@@ -12899,10 +12899,10 @@
         <v>2</v>
       </c>
       <c r="Q186" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="R186" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="S186" t="n">
         <v>12.5</v>
@@ -12966,10 +12966,10 @@
         <v>3</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="R187" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="S187" t="n">
         <v>20</v>
@@ -13033,10 +13033,10 @@
         <v>1</v>
       </c>
       <c r="Q188" t="n">
-        <v>1.010866009101286</v>
+        <v>0.9336069641199739</v>
       </c>
       <c r="R188" t="n">
-        <v>0.1920645417292444</v>
+        <v>0.177385323182795</v>
       </c>
       <c r="S188" t="n">
         <v>9</v>
@@ -13082,7 +13082,7 @@
         <v>4</v>
       </c>
       <c r="K189" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="L189" t="n">
         <v>0.85</v>
@@ -13094,16 +13094,16 @@
         <v>0.29</v>
       </c>
       <c r="O189" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="P189" t="n">
         <v>2</v>
       </c>
       <c r="Q189" t="n">
-        <v>1.347821345468382</v>
+        <v>1.244809285493299</v>
       </c>
       <c r="R189" t="n">
-        <v>0.2560860556389926</v>
+        <v>0.2365137642437267</v>
       </c>
       <c r="S189" t="n">
         <v>12</v>
@@ -13158,19 +13158,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N190" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="O190" t="n">
-        <v>0.654</v>
+        <v>0.7065</v>
       </c>
       <c r="P190" t="n">
         <v>3</v>
       </c>
       <c r="Q190" t="n">
-        <v>2.021732018202572</v>
+        <v>1.867213928239948</v>
       </c>
       <c r="R190" t="n">
-        <v>0.3841290834584888</v>
+        <v>0.3547706463655901</v>
       </c>
       <c r="S190" t="n">
         <v>18</v>
@@ -13234,10 +13234,10 @@
         <v>1</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.955323920689128</v>
+        <v>0.8995966919822622</v>
       </c>
       <c r="R191" t="n">
-        <v>0.1815115449309343</v>
+        <v>0.1709233714766298</v>
       </c>
       <c r="S191" t="n">
         <v>6</v>
@@ -13301,10 +13301,10 @@
         <v>2</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="R192" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -13350,7 +13350,7 @@
         <v>8</v>
       </c>
       <c r="K193" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L193" t="n">
         <v>0.74</v>
@@ -13362,16 +13362,16 @@
         <v>0.76</v>
       </c>
       <c r="O193" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="P193" t="n">
         <v>3</v>
       </c>
       <c r="Q193" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="R193" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="S193" t="n">
         <v>16</v>
@@ -13435,10 +13435,10 @@
         <v>1</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="R194" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="S194" t="n">
         <v>7.5</v>
@@ -13502,10 +13502,10 @@
         <v>2</v>
       </c>
       <c r="Q195" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="R195" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="S195" t="n">
         <v>12.5</v>
@@ -13569,10 +13569,10 @@
         <v>3</v>
       </c>
       <c r="Q196" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="R196" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="S196" t="n">
         <v>20</v>
@@ -13636,10 +13636,10 @@
         <v>3</v>
       </c>
       <c r="Q197" t="n">
-        <v>0.636882613792752</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="R197" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="S197" t="n">
         <v>6</v>
@@ -13703,10 +13703,10 @@
         <v>2</v>
       </c>
       <c r="Q198" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="R198" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -13770,10 +13770,10 @@
         <v>1</v>
       </c>
       <c r="Q199" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="R199" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="S199" t="n">
         <v>16</v>
@@ -13837,10 +13837,10 @@
         <v>1</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.9812435619481353</v>
+        <v>0.9147781961482522</v>
       </c>
       <c r="R200" t="n">
-        <v>0.1864362767701457</v>
+        <v>0.1738078572681679</v>
       </c>
       <c r="S200" t="n">
         <v>7.5</v>
@@ -13904,10 +13904,10 @@
         <v>2</v>
       </c>
       <c r="Q201" t="n">
-        <v>1.635405936580226</v>
+        <v>1.524630326913754</v>
       </c>
       <c r="R201" t="n">
-        <v>0.3107271279502429</v>
+        <v>0.2896797621136132</v>
       </c>
       <c r="S201" t="n">
         <v>12.5</v>
@@ -13953,7 +13953,7 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="L202" t="n">
         <v>0.71</v>
@@ -13965,16 +13965,16 @@
         <v>0.31</v>
       </c>
       <c r="O202" t="n">
-        <v>0.673</v>
+        <v>0.676</v>
       </c>
       <c r="P202" t="n">
         <v>3</v>
       </c>
       <c r="Q202" t="n">
-        <v>2.289568311212316</v>
+        <v>2.134482457679255</v>
       </c>
       <c r="R202" t="n">
-        <v>0.43501797913034</v>
+        <v>0.4055516669590585</v>
       </c>
       <c r="S202" t="n">
         <v>17.5</v>
@@ -14038,10 +14038,10 @@
         <v>3</v>
       </c>
       <c r="Q203" t="n">
-        <v>0.7331555670404936</v>
+        <v>0.6807608636383572</v>
       </c>
       <c r="R203" t="n">
-        <v>0.1392995577376938</v>
+        <v>0.1293445640912879</v>
       </c>
       <c r="S203" t="n">
         <v>6</v>
@@ -14105,10 +14105,10 @@
         <v>2</v>
       </c>
       <c r="Q204" t="n">
-        <v>1.221925945067489</v>
+        <v>1.134601439397262</v>
       </c>
       <c r="R204" t="n">
-        <v>0.232165929562823</v>
+        <v>0.2155742734854798</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -14172,10 +14172,10 @@
         <v>1</v>
       </c>
       <c r="Q205" t="n">
-        <v>1.955081512107983</v>
+        <v>1.815362303035619</v>
       </c>
       <c r="R205" t="n">
-        <v>0.3714654873005167</v>
+        <v>0.3449188375767677</v>
       </c>
       <c r="S205" t="n">
         <v>16</v>
@@ -14239,10 +14239,10 @@
         <v>1</v>
       </c>
       <c r="Q206" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="R206" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="S206" t="n">
         <v>7.5</v>
@@ -14306,10 +14306,10 @@
         <v>2</v>
       </c>
       <c r="Q207" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="R207" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="S207" t="n">
         <v>12.5</v>
@@ -14373,10 +14373,10 @@
         <v>3</v>
       </c>
       <c r="Q208" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R208" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S208" t="n">
         <v>20</v>
@@ -14440,10 +14440,10 @@
         <v>3</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.6739106727341909</v>
+        <v>0.6224046427466493</v>
       </c>
       <c r="R209" t="n">
-        <v>0.1280430278194963</v>
+        <v>0.1182568821218634</v>
       </c>
       <c r="S209" t="n">
         <v>6</v>
@@ -14507,10 +14507,10 @@
         <v>2</v>
       </c>
       <c r="Q210" t="n">
-        <v>1.123184454556985</v>
+        <v>1.037341071244415</v>
       </c>
       <c r="R210" t="n">
-        <v>0.2134050463658271</v>
+        <v>0.1970948035364389</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -14574,10 +14574,10 @@
         <v>1</v>
       </c>
       <c r="Q211" t="n">
-        <v>1.572458236379779</v>
+        <v>1.452277499742181</v>
       </c>
       <c r="R211" t="n">
-        <v>0.298767064912158</v>
+        <v>0.2759327249510145</v>
       </c>
       <c r="S211" t="n">
         <v>14</v>
@@ -14641,10 +14641,10 @@
         <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.9108902499594012</v>
+        <v>0.8558295263134812</v>
       </c>
       <c r="R212" t="n">
-        <v>0.1730691474922862</v>
+        <v>0.1626076099995614</v>
       </c>
       <c r="S212" t="n">
         <v>6</v>
@@ -14708,10 +14708,10 @@
         <v>2</v>
       </c>
       <c r="Q213" t="n">
-        <v>1.366335374939102</v>
+        <v>1.283744289470222</v>
       </c>
       <c r="R213" t="n">
-        <v>0.2596037212384293</v>
+        <v>0.2439114149993421</v>
       </c>
       <c r="S213" t="n">
         <v>9</v>
@@ -14775,10 +14775,10 @@
         <v>1</v>
       </c>
       <c r="Q214" t="n">
-        <v>2.277225624898503</v>
+        <v>2.139573815783703</v>
       </c>
       <c r="R214" t="n">
-        <v>0.4326728687307156</v>
+        <v>0.4065190249989036</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -14842,10 +14842,10 @@
         <v>1</v>
       </c>
       <c r="Q215" t="n">
-        <v>1.145401289921848</v>
+        <v>1.073023777377649</v>
       </c>
       <c r="R215" t="n">
-        <v>0.2176262450851512</v>
+        <v>0.2038745177017533</v>
       </c>
       <c r="S215" t="n">
         <v>8</v>
@@ -14909,10 +14909,10 @@
         <v>2</v>
       </c>
       <c r="Q216" t="n">
-        <v>1.718101934882773</v>
+        <v>1.609535666066473</v>
       </c>
       <c r="R216" t="n">
-        <v>0.3264393676277268</v>
+        <v>0.3058117765526299</v>
       </c>
       <c r="S216" t="n">
         <v>12</v>
@@ -14976,10 +14976,10 @@
         <v>3</v>
       </c>
       <c r="Q217" t="n">
-        <v>2.863503224804621</v>
+        <v>2.682559443444122</v>
       </c>
       <c r="R217" t="n">
-        <v>0.544065612712878</v>
+        <v>0.5096862942543832</v>
       </c>
       <c r="S217" t="n">
         <v>20</v>
@@ -15043,10 +15043,10 @@
         <v>2</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.8072116849233715</v>
+        <v>0.7537061397529922</v>
       </c>
       <c r="R218" t="n">
-        <v>0.1533702201354406</v>
+        <v>0.1432041665530685</v>
       </c>
       <c r="S218" t="n">
         <v>6</v>
@@ -15110,10 +15110,10 @@
         <v>3</v>
       </c>
       <c r="Q219" t="n">
-        <v>1.345352808205619</v>
+        <v>1.25617689958832</v>
       </c>
       <c r="R219" t="n">
-        <v>0.2556170335590677</v>
+        <v>0.2386736109217809</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -15177,10 +15177,10 @@
         <v>1</v>
       </c>
       <c r="Q220" t="n">
-        <v>2.152564493128991</v>
+        <v>2.009883039341312</v>
       </c>
       <c r="R220" t="n">
-        <v>0.4089872536945083</v>
+        <v>0.3818777774748494</v>
       </c>
       <c r="S220" t="n">
         <v>16</v>
@@ -15244,10 +15244,10 @@
         <v>1</v>
       </c>
       <c r="Q221" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="R221" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="S221" t="n">
         <v>7.5</v>
@@ -15311,10 +15311,10 @@
         <v>2</v>
       </c>
       <c r="Q222" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="R222" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="S222" t="n">
         <v>12.5</v>
@@ -15378,10 +15378,10 @@
         <v>3</v>
       </c>
       <c r="Q223" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="R223" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -15445,10 +15445,10 @@
         <v>1</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.9331070853242645</v>
+        <v>0.8777131091478716</v>
       </c>
       <c r="R224" t="n">
-        <v>0.1772903462116102</v>
+        <v>0.1667654907380956</v>
       </c>
       <c r="S224" t="n">
         <v>6</v>
@@ -15512,10 +15512,10 @@
         <v>2</v>
       </c>
       <c r="Q225" t="n">
-        <v>1.555178475540441</v>
+        <v>1.462855181913119</v>
       </c>
       <c r="R225" t="n">
-        <v>0.2954839103526837</v>
+        <v>0.2779424845634927</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
         <v>3</v>
       </c>
       <c r="Q226" t="n">
-        <v>2.488285560864705</v>
+        <v>2.340568291060991</v>
       </c>
       <c r="R226" t="n">
-        <v>0.472774256564294</v>
+        <v>0.4447079753015883</v>
       </c>
       <c r="S226" t="n">
         <v>16</v>
@@ -15646,10 +15646,10 @@
         <v>1</v>
       </c>
       <c r="Q227" t="n">
-        <v>0.9349584882713364</v>
+        <v>0.8691873985766052</v>
       </c>
       <c r="R227" t="n">
-        <v>0.1776421127715539</v>
+        <v>0.165145605729555</v>
       </c>
       <c r="S227" t="n">
         <v>7.5</v>
@@ -15695,7 +15695,7 @@
         <v>5</v>
       </c>
       <c r="K228" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="L228" t="n">
         <v>0.83</v>
@@ -15707,16 +15707,16 @@
         <v>0.35</v>
       </c>
       <c r="O228" t="n">
-        <v>0.735</v>
+        <v>0.738</v>
       </c>
       <c r="P228" t="n">
         <v>2</v>
       </c>
       <c r="Q228" t="n">
-        <v>1.558264147118894</v>
+        <v>1.448645664294342</v>
       </c>
       <c r="R228" t="n">
-        <v>0.2960701879525898</v>
+        <v>0.275242676215925</v>
       </c>
       <c r="S228" t="n">
         <v>12.5</v>
@@ -15780,10 +15780,10 @@
         <v>3</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.49322263539023</v>
+        <v>2.317833062870947</v>
       </c>
       <c r="R229" t="n">
-        <v>0.4737123007241438</v>
+        <v>0.44038828194548</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -15847,10 +15847,10 @@
         <v>1</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.8812678028062497</v>
+        <v>0.8266514158676271</v>
       </c>
       <c r="R230" t="n">
-        <v>0.1674408825331875</v>
+        <v>0.1570637690148492</v>
       </c>
       <c r="S230" t="n">
         <v>6</v>
@@ -15914,10 +15914,10 @@
         <v>2</v>
       </c>
       <c r="Q231" t="n">
-        <v>1.46877967134375</v>
+        <v>1.377752359779379</v>
       </c>
       <c r="R231" t="n">
-        <v>0.2790681375553124</v>
+        <v>0.261772948358082</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -15981,10 +15981,10 @@
         <v>3</v>
       </c>
       <c r="Q232" t="n">
-        <v>2.350047474149999</v>
+        <v>2.204403775647006</v>
       </c>
       <c r="R232" t="n">
-        <v>0.4465090200884999</v>
+        <v>0.4188367173729311</v>
       </c>
       <c r="S232" t="n">
         <v>16</v>
@@ -16030,7 +16030,7 @@
         <v>4</v>
       </c>
       <c r="K233" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="L233" t="n">
         <v>0.79</v>
@@ -16042,16 +16042,16 @@
         <v>0.15</v>
       </c>
       <c r="O233" t="n">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
       </c>
       <c r="Q233" t="n">
-        <v>2.229089148274632</v>
+        <v>2.099058947958611</v>
       </c>
       <c r="R233" t="n">
-        <v>0.4235269381721801</v>
+        <v>0.3988212001121362</v>
       </c>
       <c r="S233" t="n">
         <v>14</v>
@@ -16115,10 +16115,10 @@
         <v>2</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.343633722411948</v>
+        <v>3.148588421937917</v>
       </c>
       <c r="R234" t="n">
-        <v>0.6352904072582701</v>
+        <v>0.5982318001682043</v>
       </c>
       <c r="S234" t="n">
         <v>21</v>
@@ -16182,10 +16182,10 @@
         <v>3</v>
       </c>
       <c r="Q235" t="n">
-        <v>4.458178296549264</v>
+        <v>4.198117895917223</v>
       </c>
       <c r="R235" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7976424002242724</v>
       </c>
       <c r="S235" t="n">
         <v>28</v>
@@ -16249,10 +16249,10 @@
         <v>3</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.6368826137927521</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="R236" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="S236" t="n">
         <v>6</v>
@@ -16316,10 +16316,10 @@
         <v>1</v>
       </c>
       <c r="Q237" t="n">
-        <v>1.114544574137316</v>
+        <v>1.025381008206331</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2117634690860901</v>
+        <v>0.1948223915592028</v>
       </c>
       <c r="S237" t="n">
         <v>10.5</v>
@@ -16383,10 +16383,10 @@
         <v>2</v>
       </c>
       <c r="Q238" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="R238" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -16432,7 +16432,7 @@
         <v>5</v>
       </c>
       <c r="K239" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="L239" t="n">
         <v>0.83</v>
@@ -16444,16 +16444,16 @@
         <v>0.15</v>
       </c>
       <c r="O239" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
       </c>
       <c r="Q239" t="n">
-        <v>1.86683130496422</v>
+        <v>1.752584314771988</v>
       </c>
       <c r="R239" t="n">
-        <v>0.3546979479432018</v>
+        <v>0.3329910198066777</v>
       </c>
       <c r="S239" t="n">
         <v>12.5</v>
@@ -16517,10 +16517,10 @@
         <v>2</v>
       </c>
       <c r="Q240" t="n">
-        <v>2.986930087942751</v>
+        <v>2.80413490363518</v>
       </c>
       <c r="R240" t="n">
-        <v>0.5675167167091227</v>
+        <v>0.5327856316906843</v>
       </c>
       <c r="S240" t="n">
         <v>20</v>
@@ -16584,10 +16584,10 @@
         <v>3</v>
       </c>
       <c r="Q241" t="n">
-        <v>4.480395131914127</v>
+        <v>4.206202355452771</v>
       </c>
       <c r="R241" t="n">
-        <v>0.8512750750636842</v>
+        <v>0.7991784475360264</v>
       </c>
       <c r="S241" t="n">
         <v>30</v>
